--- a/artfynd/A 1518-2025 artfynd.xlsx
+++ b/artfynd/A 1518-2025 artfynd.xlsx
@@ -675,52 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102339788</v>
+        <v>102339847</v>
       </c>
       <c r="B2" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561645</v>
+        <v>561599</v>
       </c>
       <c r="R2" t="n">
-        <v>6704987</v>
+        <v>6705019</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,12 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>100-tal bladrosetter</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,12 +786,7 @@
         <v>102339902</v>
       </c>
       <c r="B3" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102339795</v>
+        <v>102339768</v>
       </c>
       <c r="B4" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561631</v>
+        <v>561645</v>
       </c>
       <c r="R4" t="n">
-        <v>6704992</v>
+        <v>6704987</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102339869</v>
+        <v>102339795</v>
       </c>
       <c r="B5" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561621</v>
+        <v>561631</v>
       </c>
       <c r="R5" t="n">
-        <v>6704978</v>
+        <v>6704992</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,7 +1072,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,41 +1109,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102339847</v>
+        <v>102339854</v>
       </c>
       <c r="B6" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
@@ -1248,15 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102339854</v>
+        <v>102339869</v>
       </c>
       <c r="B7" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561599</v>
+        <v>561621</v>
       </c>
       <c r="R7" t="n">
-        <v>6705019</v>
+        <v>6704978</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,12 +1330,7 @@
         <v>102339896</v>
       </c>
       <c r="B8" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,12 +1443,7 @@
         <v>102339967</v>
       </c>
       <c r="B9" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1518-2025 artfynd.xlsx
+++ b/artfynd/A 1518-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102339847</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102339902</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102339768</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102339795</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102339854</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102339869</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102339896</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,8 +1590,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102339967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>